--- a/气象/蒙古气象/蒙古91-20气温统计详细表.xlsx
+++ b/气象/蒙古气象/蒙古91-20气温统计详细表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古相关\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\蒙古气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2330E77-D7DB-49C3-89DA-B3376C1B0FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1E2181-7328-4437-84B5-A98359C1B325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E93861B9-CD70-4C8D-B866-011E4AE1EA5C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{E93861B9-CD70-4C8D-B866-011E4AE1EA5C}"/>
   </bookViews>
   <sheets>
     <sheet name="月平均气温" sheetId="1" r:id="rId1"/>
@@ -1593,7 +1593,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1695,6 +1695,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1772,7 +1781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1797,6 +1806,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1815,7 +1827,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2149,26 +2161,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
@@ -10716,7 +10728,7 @@
       <c r="A159" s="7">
         <v>157</v>
       </c>
-      <c r="B159" s="14" t="s">
+      <c r="B159" s="8" t="s">
         <v>430</v>
       </c>
       <c r="C159" s="6" t="s">
@@ -19536,26 +19548,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -36920,26 +36932,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -41639,7 +41651,7 @@
       <c r="K88" s="2">
         <v>40.4</v>
       </c>
-      <c r="L88" s="2">
+      <c r="L88" s="15">
         <v>44.5</v>
       </c>
       <c r="M88" s="2">

--- a/气象/蒙古气象/蒙古91-20气温统计详细表.xlsx
+++ b/气象/蒙古气象/蒙古91-20气温统计详细表.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF1E2181-7328-4437-84B5-A98359C1B325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{E93861B9-CD70-4C8D-B866-011E4AE1EA5C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E93861B9-CD70-4C8D-B866-011E4AE1EA5C}"/>
   </bookViews>
   <sheets>
     <sheet name="月平均气温" sheetId="1" r:id="rId1"/>
@@ -1809,6 +1809,15 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1820,15 +1829,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2161,26 +2161,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="12" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
@@ -19548,26 +19548,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -36932,26 +36932,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
     </row>
     <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
@@ -41651,7 +41651,7 @@
       <c r="K88" s="2">
         <v>40.4</v>
       </c>
-      <c r="L88" s="15">
+      <c r="L88" s="9">
         <v>44.5</v>
       </c>
       <c r="M88" s="2">
